--- a/publication_materials/tables/publication_supplementary_tables.xlsx
+++ b/publication_materials/tables/publication_supplementary_tables.xlsx
@@ -7577,7 +7577,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -7655,7 +7655,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -7733,7 +7733,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7811,7 +7811,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7889,7 +7889,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7967,7 +7967,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -8045,7 +8045,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -8201,7 +8201,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -8279,7 +8279,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -8357,7 +8357,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -8435,7 +8435,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -8513,7 +8513,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -8591,7 +8591,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -8669,7 +8669,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -8747,7 +8747,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -8825,7 +8825,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -8903,7 +8903,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -8981,7 +8981,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -9059,7 +9059,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -9137,7 +9137,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -9215,7 +9215,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -9293,7 +9293,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -9449,7 +9449,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -9527,7 +9527,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -9605,7 +9605,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>RandomForest_SMOTE</t>
+          <t>RandomForest_NoClassWeight</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">

--- a/publication_materials/tables/publication_supplementary_tables.xlsx
+++ b/publication_materials/tables/publication_supplementary_tables.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="S1_dataset_statistics" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="S2_hyperparameter_search" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="S3_full_performance" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="S4_SHAP_top20" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="S4b_SHAP_interpretation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="S5_malaysia_per_class" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="S5b_malaysia_per_sector" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="S5c_johor_2019" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="S0_label_schema" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S1_dataset_statistics" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S2_hyperparameter_search" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S3_full_performance" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4_SHAP_top20" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S4b_SHAP_interpretation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5_malaysia_per_class" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5b_malaysia_per_sector" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5c_johor_2019" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S0_label_schema" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/publication_materials/tables/publication_supplementary_tables.xlsx
+++ b/publication_materials/tables/publication_supplementary_tables.xlsx
@@ -16,6 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5b_malaysia_per_sector" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S5c_johor_2019" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S0_label_schema" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="S6_relabel_audit" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -803,6 +804,502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>column</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>expected_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>cid</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>live_pictograms</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>outcome</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GHS07_Irritant</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>23668352</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Sodium n-heptyl sulfate</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GHS07_Irritant</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>13270780</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2-((4-Methylphenyl)methoxy)acetic acid</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GHS07_Irritant</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>16427083</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2-Amino-4-(methoxycarbonyl)benzeneboronic acid hydrochloride</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GHS07_Irritant</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>35751</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2-(4-Acetylphenoxy)-1-(1-piperidinyl)ethanone</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GHS07_Irritant</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>85743515</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Tert-butyl 2-(2-formyl-6-methoxyphenoxy)acetate</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>GHS07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GHS08_HealthHazard</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>71309877</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>N-Ethyl-d5-maleimide</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>GHS05,GHS06,GHS08</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GHS08_HealthHazard</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>7010559</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>H-Leu-ala-betana</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GHS08_HealthHazard</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>444865</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Equilenin</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GHS08_HealthHazard</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>5453</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Thiotepa</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>GHS06,GHS07,GHS08</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>GHS08_HealthHazard</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>118984441</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Teriparatide acetate hydrate</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>GHS08</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>GHS09_Environmental</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>51060846</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4-(Allyloxy)-N'-(2-methyl-3-phenyl-2-propenylidene)benzohydrazide</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>GHS09_Environmental</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>57330099</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2-Isopropylphenyl (2-(naphthalen-2-yl)ethyl)carbamate</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GHS06,GHS09</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>GHS09_Environmental</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>4064248</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Naphthyl methacrylate</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>GHS09_Environmental</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>11337568</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Poly(oxy-1,2-ethanediyl), alpha-acetyl-omega-(3-(1,3,3,3-tetramethyl-1-((trimethylsilyl)oxy)disiloxanyl)propoxy)-</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>GHS09_Environmental</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>9679019</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4-(2-((1-Naphthyloxy)acetyl)carbohydrazonoyl)phenyl 3-bromobenzoate</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GHS09</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -16887,7 +17384,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -16941,7 +17438,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -16995,7 +17492,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17049,7 +17546,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -17103,7 +17600,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -17157,7 +17654,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17265,7 +17762,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17319,7 +17816,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17373,7 +17870,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17924,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17481,7 +17978,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -17535,7 +18032,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17589,7 +18086,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -17643,7 +18140,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17697,7 +18194,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17751,7 +18248,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -17967,7 +18464,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18021,7 +18518,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18075,7 +18572,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18129,7 +18626,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18183,7 +18680,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18237,7 +18734,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18291,7 +18788,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18345,7 +18842,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18896,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18453,7 +18950,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18507,7 +19004,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18561,7 +19058,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18615,7 +19112,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18669,7 +19166,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18777,7 +19274,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18831,7 +19328,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18885,7 +19382,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -18939,7 +19436,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -18993,7 +19490,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -19101,7 +19598,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -19155,7 +19652,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -19209,7 +19706,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not among the classically expected bulk descriptors for this class; likely a secondary or class-specific contributor</t>
         </is>
       </c>
     </row>
@@ -19263,7 +19760,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>not among the classically expected bulk descriptors; likely acting as a structural marker</t>
+          <t>not evaluated by this check - it covers bulk physicochemical descriptors only; see Chemical Interpretation for this substructure's relevance</t>
         </is>
       </c>
     </row>
@@ -19347,19 +19844,31 @@
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -19380,20 +19889,30 @@
       <c r="D3" t="n">
         <v>28</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.8837</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.871</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.9643</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0.9153</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.7413</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.8837</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.9643</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.9153</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.7413</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -19415,20 +19934,30 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -19450,20 +19979,30 @@
       <c r="D5" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.9535</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.9091</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.8848</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0.9535</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0.8333</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.9091</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.8848</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -19485,20 +20024,30 @@
       <c r="D6" t="n">
         <v>14</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.8605</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.7143</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.7692</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0.6742</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.8605</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.8333</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.7143</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.7692</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.6742</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -19520,20 +20069,30 @@
       <c r="D7" t="n">
         <v>16</v>
       </c>
-      <c r="E7" t="n">
-        <v>0.7907</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.6522</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.7692</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.6214</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0.7907</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0.6522</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.9375</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.7692</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.6214</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -19555,20 +20114,30 @@
       <c r="D8" t="n">
         <v>37</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.8605</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.9429</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.8919</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.9167</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4974</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0.8605</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0.9429</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.8919</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.9167</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.4974</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -19590,20 +20159,30 @@
       <c r="D9" t="n">
         <v>36</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.7674</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.8611</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.8611</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.8611</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.1468</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0.7674</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.8611</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.8611</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.8611</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.1468</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -19625,20 +20204,30 @@
       <c r="D10" t="n">
         <v>25</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.4884</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.2667</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.1607</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.4884</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.16</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.2667</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.1607</t>
+        </is>
       </c>
     </row>
   </sheetData>
